--- a/artfynd/A 69068-2021 artfynd.xlsx
+++ b/artfynd/A 69068-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69068-2021 artfynd.xlsx
+++ b/artfynd/A 69068-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>97683660</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588193.2330786253</v>
+        <v>588193</v>
       </c>
       <c r="R2" t="n">
-        <v>6591099.297433948</v>
+        <v>6591099</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -791,12 +786,7 @@
         <v>99102866</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588174.3981320052</v>
+        <v>588174</v>
       </c>
       <c r="R3" t="n">
-        <v>6591142.093506349</v>
+        <v>6591142</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 69068-2021 artfynd.xlsx
+++ b/artfynd/A 69068-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97683660</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99102866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>